--- a/templates/_masters/LGL-003-guest-screening-log-DEMO.xlsx
+++ b/templates/_masters/LGL-003-guest-screening-log-DEMO.xlsx
@@ -527,7 +527,7 @@
     <dxf>
       <font>
         <b val="1"/>
-        <color rgb="000F5132"/>
+        <color rgb="00166534"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -542,7 +542,7 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F8D7DA"/>
+          <fgColor rgb="00FFCCCC"/>
         </patternFill>
       </fill>
     </dxf>
